--- a/Profit Amount/sales_data.xlsx
+++ b/Profit Amount/sales_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Profit Amount\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E62ECFB-8AB0-4160-AF91-2F13866A08D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA0AA46-2262-424E-8083-E568F33A2BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,9 +76,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B353"/>
+  <dimension ref="A1:C352"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.3984375" bestFit="1" customWidth="1"/>
@@ -445,7 +446,7 @@
         <v>2960184</v>
       </c>
       <c r="B3" s="1">
-        <v>15151.990000000009</v>
+        <v>16095.420000000015</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -453,7 +454,7 @@
         <v>2960222</v>
       </c>
       <c r="B4" s="1">
-        <v>12121.592000000006</v>
+        <v>12876.336000000012</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -461,7 +462,7 @@
         <v>7427213</v>
       </c>
       <c r="B5" s="1">
-        <v>4903.2832000000008</v>
+        <v>5184.1232000000009</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -469,7 +470,7 @@
         <v>7428213</v>
       </c>
       <c r="B6" s="1">
-        <v>6651.6232000000009</v>
+        <v>6684.6632000000009</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -477,7 +478,7 @@
         <v>7600184</v>
       </c>
       <c r="B7" s="1">
-        <v>5082.3900000000031</v>
+        <v>5105.9900000000034</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -485,7 +486,7 @@
         <v>7600203</v>
       </c>
       <c r="B8" s="1">
-        <v>2740.2156000000014</v>
+        <v>2867.6556000000014</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -493,7 +494,7 @@
         <v>7670213</v>
       </c>
       <c r="B9" s="1">
-        <v>3654.2980000000007</v>
+        <v>3687.3380000000006</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -501,7 +502,7 @@
         <v>7688203</v>
       </c>
       <c r="B10" s="1">
-        <v>3131.8080000000009</v>
+        <v>3315.8880000000008</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -509,7 +510,7 @@
         <v>7688213</v>
       </c>
       <c r="B11" s="1">
-        <v>3656.3736000000017</v>
+        <v>3871.1336000000015</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -549,7 +550,7 @@
         <v>2968213</v>
       </c>
       <c r="B16" s="1">
-        <v>4422.5208000000011</v>
+        <v>4439.0408000000007</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -573,7 +574,7 @@
         <v>7420213</v>
       </c>
       <c r="B19" s="1">
-        <v>4807.25</v>
+        <v>5137.6500000000005</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -581,7 +582,7 @@
         <v>7420222</v>
       </c>
       <c r="B20" s="1">
-        <v>5494.720000000003</v>
+        <v>5872.3200000000033</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -589,7 +590,7 @@
         <v>7421234</v>
       </c>
       <c r="B21" s="1">
-        <v>7427.8400000000056</v>
+        <v>7899.8400000000065</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -597,7 +598,7 @@
         <v>7477203</v>
       </c>
       <c r="B22" s="1">
-        <v>3921.8640000000019</v>
+        <v>4148.4240000000018</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -621,7 +622,7 @@
         <v>7638234</v>
       </c>
       <c r="B25" s="1">
-        <v>6656.9600000000046</v>
+        <v>6916.5600000000049</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -645,7 +646,7 @@
         <v>7267234</v>
       </c>
       <c r="B28" s="1">
-        <v>16048.19000000001</v>
+        <v>16520.19000000001</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -653,7 +654,7 @@
         <v>7264222</v>
       </c>
       <c r="B29" s="1">
-        <v>5663.8816000000043</v>
+        <v>5943.8720000000039</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -661,7 +662,7 @@
         <v>7265234</v>
       </c>
       <c r="B30" s="1">
-        <v>10241.952000000008</v>
+        <v>10771.536000000007</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -669,7 +670,7 @@
         <v>7677282</v>
       </c>
       <c r="B31" s="1">
-        <v>2722.2200000000003</v>
+        <v>2929.9000000000005</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -677,7 +678,7 @@
         <v>7677283</v>
       </c>
       <c r="B32" s="1">
-        <v>3919.82</v>
+        <v>4221.9000000000005</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -685,7 +686,7 @@
         <v>7677184</v>
       </c>
       <c r="B33" s="1">
-        <v>5158.1600000000044</v>
+        <v>5417.7600000000048</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -709,7 +710,7 @@
         <v>2927152</v>
       </c>
       <c r="B36" s="1">
-        <v>4867.0919999999987</v>
+        <v>4994.5319999999992</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -717,7 +718,7 @@
         <v>2927184</v>
       </c>
       <c r="B37" s="1">
-        <v>5407.8800000000037</v>
+        <v>5549.4800000000041</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -725,7 +726,7 @@
         <v>2933156</v>
       </c>
       <c r="B38" s="1">
-        <v>4158.2879999999996</v>
+        <v>4554.768</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -733,7 +734,7 @@
         <v>1404184</v>
       </c>
       <c r="B39" s="1">
-        <v>5484.4400000000032</v>
+        <v>6499.6000000000049</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -741,7 +742,7 @@
         <v>1404234</v>
       </c>
       <c r="B40" s="1">
-        <v>5407.7600000000029</v>
+        <v>6422.8000000000056</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -749,7 +750,7 @@
         <v>1404242</v>
       </c>
       <c r="B41" s="1">
-        <v>2692.5200000000018</v>
+        <v>3199.8000000000015</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -757,7 +758,7 @@
         <v>1404265</v>
       </c>
       <c r="B42" s="1">
-        <v>5330.7900000000045</v>
+        <v>6345.4800000000041</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -765,7 +766,7 @@
         <v>5034184</v>
       </c>
       <c r="B43" s="1">
-        <v>3893.0000000000023</v>
+        <v>4445.3500000000031</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -773,7 +774,7 @@
         <v>5034203</v>
       </c>
       <c r="B44" s="1">
-        <v>2305.3100000000013</v>
+        <v>2900.1440000000011</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -781,7 +782,7 @@
         <v>5034229</v>
       </c>
       <c r="B45" s="1">
-        <v>3892.9999999999995</v>
+        <v>4884.01</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -789,7 +790,7 @@
         <v>7231256</v>
       </c>
       <c r="B46" s="1">
-        <v>3689.7375000000015</v>
+        <v>4415.4900000000034</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
@@ -797,7 +798,7 @@
         <v>7429184</v>
       </c>
       <c r="B47" s="1">
-        <v>5247.4500000000035</v>
+        <v>6238.6400000000049</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
@@ -805,7 +806,7 @@
         <v>7429240</v>
       </c>
       <c r="B48" s="1">
-        <v>5239.1499999999996</v>
+        <v>6230.3600000000006</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -813,7 +814,7 @@
         <v>7429244</v>
       </c>
       <c r="B49" s="1">
-        <v>6280.0959999999995</v>
+        <v>7157.8559999999998</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -821,7 +822,7 @@
         <v>7429297</v>
       </c>
       <c r="B50" s="1">
-        <v>1809.5275000000001</v>
+        <v>2139.94</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -829,7 +830,7 @@
         <v>7430184</v>
       </c>
       <c r="B51" s="1">
-        <v>5515.6800000000048</v>
+        <v>6506.5000000000055</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -837,7 +838,7 @@
         <v>7430234</v>
       </c>
       <c r="B52" s="1">
-        <v>5074.0100000000039</v>
+        <v>6348.480000000005</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -845,7 +846,7 @@
         <v>7430240</v>
       </c>
       <c r="B53" s="1">
-        <v>5192.01</v>
+        <v>6348.4800000000005</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -853,7 +854,7 @@
         <v>7430296</v>
       </c>
       <c r="B54" s="1">
-        <v>1704.894</v>
+        <v>2142.56</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -861,7 +862,7 @@
         <v>7430297</v>
       </c>
       <c r="B55" s="1">
-        <v>1746.194</v>
+        <v>2142.56</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -869,7 +870,7 @@
         <v>7434256</v>
       </c>
       <c r="B56" s="1">
-        <v>3707.7525000000028</v>
+        <v>4539.6750000000029</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -877,7 +878,7 @@
         <v>7436184</v>
       </c>
       <c r="B57" s="1">
-        <v>5391.9500000000044</v>
+        <v>6335.7600000000048</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -885,7 +886,7 @@
         <v>7436229</v>
       </c>
       <c r="B58" s="1">
-        <v>5580.75</v>
+        <v>6524.56</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -893,7 +894,7 @@
         <v>7436250</v>
       </c>
       <c r="B59" s="1">
-        <v>1929.5632000000001</v>
+        <v>2301.0768000000003</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -901,7 +902,7 @@
         <v>7436253</v>
       </c>
       <c r="B60" s="1">
-        <v>3796.2525000000005</v>
+        <v>4539.6750000000002</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -909,7 +910,7 @@
         <v>7470184</v>
       </c>
       <c r="B61" s="1">
-        <v>4667.7300000000032</v>
+        <v>5753.8000000000038</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -917,7 +918,7 @@
         <v>7470251</v>
       </c>
       <c r="B62" s="1">
-        <v>1661.003300000001</v>
+        <v>1889.2652000000012</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -925,7 +926,7 @@
         <v>7470256</v>
       </c>
       <c r="B63" s="1">
-        <v>3309.9075000000021</v>
+        <v>3767.5350000000026</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -933,7 +934,7 @@
         <v>7472184</v>
       </c>
       <c r="B64" s="1">
-        <v>4398.4320000000025</v>
+        <v>5484.2640000000038</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -941,7 +942,7 @@
         <v>7472203</v>
       </c>
       <c r="B65" s="1">
-        <v>2592.6000000000013</v>
+        <v>3243.5820000000017</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -949,7 +950,7 @@
         <v>7472234</v>
       </c>
       <c r="B66" s="1">
-        <v>4289.6140000000032</v>
+        <v>5375.6080000000047</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -957,7 +958,7 @@
         <v>7472251</v>
       </c>
       <c r="B67" s="1">
-        <v>1535.1459000000007</v>
+        <v>1942.1073000000017</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -965,7 +966,7 @@
         <v>7472256</v>
       </c>
       <c r="B68" s="1">
-        <v>3026.7575000000011</v>
+        <v>3840.7050000000027</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
@@ -973,7 +974,7 @@
         <v>7485174</v>
       </c>
       <c r="B69" s="1">
-        <v>4751.1360000000032</v>
+        <v>5695.0640000000039</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
@@ -981,7 +982,7 @@
         <v>7485184</v>
       </c>
       <c r="B70" s="1">
-        <v>4325.2760000000035</v>
+        <v>5481.1960000000036</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
@@ -989,7 +990,7 @@
         <v>7485234</v>
       </c>
       <c r="B71" s="1">
-        <v>4015.4220000000028</v>
+        <v>5077.2200000000039</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
@@ -997,7 +998,7 @@
         <v>7485242</v>
       </c>
       <c r="B72" s="1">
-        <v>1962.3300000000013</v>
+        <v>2493.2240000000011</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -1005,7 +1006,7 @@
         <v>7485251</v>
       </c>
       <c r="B73" s="1">
-        <v>1483.5744000000011</v>
+        <v>1881.7656000000015</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
@@ -1013,7 +1014,7 @@
         <v>7485265</v>
       </c>
       <c r="B74" s="1">
-        <v>3827.5700000000029</v>
+        <v>4889.4960000000037</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
@@ -1021,7 +1022,7 @@
         <v>7489184</v>
       </c>
       <c r="B75" s="1">
-        <v>5201.5100000000048</v>
+        <v>6310.640000000004</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -1029,7 +1030,7 @@
         <v>7489203</v>
       </c>
       <c r="B76" s="1">
-        <v>3094.3700000000013</v>
+        <v>3759.8160000000016</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
@@ -1037,7 +1038,7 @@
         <v>7489234</v>
       </c>
       <c r="B77" s="1">
-        <v>5131.5700000000033</v>
+        <v>6005.0000000000036</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
@@ -1045,7 +1046,7 @@
         <v>7489241</v>
       </c>
       <c r="B78" s="1">
-        <v>2424.5200000000004</v>
+        <v>2978.9750000000004</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
@@ -1053,7 +1054,7 @@
         <v>7489250</v>
       </c>
       <c r="B79" s="1">
-        <v>1826.4528</v>
+        <v>2242.1420999999996</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
@@ -1061,7 +1062,7 @@
         <v>7489253</v>
       </c>
       <c r="B80" s="1">
-        <v>3600.9800000000005</v>
+        <v>4432.6449999999995</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
@@ -1069,7 +1070,7 @@
         <v>7489265</v>
       </c>
       <c r="B81" s="1">
-        <v>4903.1500000000033</v>
+        <v>5894.1200000000044</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
@@ -1077,7 +1078,7 @@
         <v>7494174</v>
       </c>
       <c r="B82" s="1">
-        <v>5703.104000000003</v>
+        <v>6646.6000000000031</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
@@ -1085,7 +1086,7 @@
         <v>7494184</v>
       </c>
       <c r="B83" s="1">
-        <v>5285.9400000000041</v>
+        <v>6230.2500000000045</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -1093,7 +1094,7 @@
         <v>7494234</v>
       </c>
       <c r="B84" s="1">
-        <v>5276.1600000000035</v>
+        <v>6220.3300000000045</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -1101,7 +1102,7 @@
         <v>7494242</v>
       </c>
       <c r="B85" s="1">
-        <v>2616.2010000000009</v>
+        <v>2832.2920000000013</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
@@ -1109,7 +1110,7 @@
         <v>7494251</v>
       </c>
       <c r="B86" s="1">
-        <v>1973.5200000000013</v>
+        <v>2327.5738000000015</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -1117,7 +1118,7 @@
         <v>7494265</v>
       </c>
       <c r="B87" s="1">
-        <v>5220.1800000000048</v>
+        <v>6163.9200000000046</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
@@ -1125,7 +1126,7 @@
         <v>7505195</v>
       </c>
       <c r="B88" s="1">
-        <v>2412.6871999999998</v>
+        <v>2967.0516000000007</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
@@ -1141,7 +1142,7 @@
         <v>7556184</v>
       </c>
       <c r="B90" s="1">
-        <v>5259.9400000000032</v>
+        <v>6250.8000000000047</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
@@ -1149,7 +1150,7 @@
         <v>7556203</v>
       </c>
       <c r="B91" s="1">
-        <v>2592.0060000000008</v>
+        <v>3342.2320000000018</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
@@ -1157,7 +1158,7 @@
         <v>7556204</v>
       </c>
       <c r="B92" s="1">
-        <v>2592.0059999999994</v>
+        <v>3342.2320000000004</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
@@ -1165,7 +1166,7 @@
         <v>7556234</v>
       </c>
       <c r="B93" s="1">
-        <v>4914.0000000000045</v>
+        <v>5881.100000000004</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
@@ -1173,7 +1174,7 @@
         <v>7556241</v>
       </c>
       <c r="B94" s="1">
-        <v>2130.2799999999997</v>
+        <v>2791.0650000000001</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
@@ -1181,7 +1182,7 @@
         <v>7556242</v>
       </c>
       <c r="B95" s="1">
-        <v>2130.2800000000007</v>
+        <v>2673.0650000000014</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
@@ -1189,7 +1190,7 @@
         <v>7556250</v>
       </c>
       <c r="B96" s="1">
-        <v>1592.7936</v>
+        <v>2061.8175000000001</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
@@ -1197,7 +1198,7 @@
         <v>7556251</v>
       </c>
       <c r="B97" s="1">
-        <v>1592.7936000000011</v>
+        <v>1973.3175000000015</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
@@ -1205,7 +1206,7 @@
         <v>7556253</v>
       </c>
       <c r="B98" s="1">
-        <v>3057.2775000000001</v>
+        <v>4084.1400000000003</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
@@ -1213,7 +1214,7 @@
         <v>7556265</v>
       </c>
       <c r="B99" s="1">
-        <v>4300.9800000000023</v>
+        <v>5316.1200000000035</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
@@ -1221,7 +1222,7 @@
         <v>7577174</v>
       </c>
       <c r="B100" s="1">
-        <v>5427.456000000001</v>
+        <v>6394.8960000000034</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
@@ -1229,7 +1230,7 @@
         <v>7577184</v>
       </c>
       <c r="B101" s="1">
-        <v>5261.100000000004</v>
+        <v>6228.8600000000042</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
@@ -1237,7 +1238,7 @@
         <v>7577203</v>
       </c>
       <c r="B102" s="1">
-        <v>2901.0500000000015</v>
+        <v>3552.4960000000015</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
@@ -1245,7 +1246,7 @@
         <v>7577234</v>
       </c>
       <c r="B103" s="1">
-        <v>4550.2800000000025</v>
+        <v>5683.024000000004</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
@@ -1253,7 +1254,7 @@
         <v>7577242</v>
       </c>
       <c r="B104" s="1">
-        <v>2284.7200000000007</v>
+        <v>2827.4600000000019</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
@@ -1261,7 +1262,7 @@
         <v>7577251</v>
       </c>
       <c r="B105" s="1">
-        <v>1713.4330000000011</v>
+        <v>2120.5614000000014</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
@@ -1269,7 +1270,7 @@
         <v>7577256</v>
       </c>
       <c r="B106" s="1">
-        <v>3507.0375000000026</v>
+        <v>4321.1400000000031</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
@@ -1277,7 +1278,7 @@
         <v>7577265</v>
       </c>
       <c r="B107" s="1">
-        <v>4443.4600000000037</v>
+        <v>5529.2500000000027</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
@@ -1285,7 +1286,7 @@
         <v>2502234</v>
       </c>
       <c r="B108" s="1">
-        <v>4950.1960000000036</v>
+        <v>5454.9520000000048</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
@@ -1293,7 +1294,7 @@
         <v>2502265</v>
       </c>
       <c r="B109" s="1">
-        <v>4870.7310000000034</v>
+        <v>5861.5990000000029</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
@@ -1301,7 +1302,7 @@
         <v>2503184</v>
       </c>
       <c r="B110" s="1">
-        <v>5410.7200000000039</v>
+        <v>6402.4820000000045</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
@@ -1309,7 +1310,7 @@
         <v>2503234</v>
       </c>
       <c r="B111" s="1">
-        <v>5295.3180000000038</v>
+        <v>6286.3120000000044</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
@@ -1317,7 +1318,7 @@
         <v>2503265</v>
       </c>
       <c r="B112" s="1">
-        <v>5223.7300000000041</v>
+        <v>5726.5040000000035</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
@@ -1325,7 +1326,7 @@
         <v>4906175</v>
       </c>
       <c r="B113" s="1">
-        <v>2781.9920000000011</v>
+        <v>3336.5380000000018</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
@@ -1333,7 +1334,7 @@
         <v>4906184</v>
       </c>
       <c r="B114" s="1">
-        <v>5330.6500000000042</v>
+        <v>6439.560000000004</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
@@ -1341,7 +1342,7 @@
         <v>4906234</v>
       </c>
       <c r="B115" s="1">
-        <v>5190.220000000003</v>
+        <v>6299.600000000004</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
@@ -1349,7 +1350,7 @@
         <v>7511184</v>
       </c>
       <c r="B116" s="1">
-        <v>5391.6200000000026</v>
+        <v>6383.1600000000035</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
@@ -1357,7 +1358,7 @@
         <v>7511234</v>
       </c>
       <c r="B117" s="1">
-        <v>5097.4000000000033</v>
+        <v>6088.5200000000032</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
@@ -1365,7 +1366,7 @@
         <v>7511240</v>
       </c>
       <c r="B118" s="1">
-        <v>5097.3999999999996</v>
+        <v>6088.5199999999995</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
@@ -1373,7 +1374,7 @@
         <v>7511251</v>
       </c>
       <c r="B119" s="1">
-        <v>1885.2108000000012</v>
+        <v>2257.0206000000012</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
@@ -1381,7 +1382,7 @@
         <v>7511269</v>
       </c>
       <c r="B120" s="1">
-        <v>4644.88</v>
+        <v>5636</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
@@ -1389,7 +1390,7 @@
         <v>7515184</v>
       </c>
       <c r="B121" s="1">
-        <v>6024.9100000000053</v>
+        <v>7015.860000000006</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
@@ -1397,7 +1398,7 @@
         <v>7515240</v>
       </c>
       <c r="B122" s="1">
-        <v>5683.6</v>
+        <v>6184.28</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
@@ -1405,7 +1406,7 @@
         <v>7515265</v>
       </c>
       <c r="B123" s="1">
-        <v>5241.8050000000039</v>
+        <v>6232.7600000000039</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
@@ -1413,7 +1414,7 @@
         <v>7515269</v>
       </c>
       <c r="B124" s="1">
-        <v>5241.8050000000003</v>
+        <v>6232.7599999999993</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
@@ -1421,7 +1422,7 @@
         <v>3723213</v>
       </c>
       <c r="B125" s="1">
-        <v>3202.6056000000012</v>
+        <v>3541.7424000000005</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
@@ -1429,7 +1430,7 @@
         <v>3725213</v>
       </c>
       <c r="B126" s="1">
-        <v>2505.3480000000009</v>
+        <v>3315.0212000000015</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
@@ -1437,7 +1438,7 @@
         <v>4950184</v>
       </c>
       <c r="B127" s="1">
-        <v>4674.0800000000045</v>
+        <v>5641.6100000000042</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
@@ -1445,7 +1446,7 @@
         <v>4950234</v>
       </c>
       <c r="B128" s="1">
-        <v>4108.2400000000034</v>
+        <v>5217.3600000000042</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
@@ -1453,7 +1454,7 @@
         <v>4950269</v>
       </c>
       <c r="B129" s="1">
-        <v>4032.152000000001</v>
+        <v>4647.1839999999984</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
@@ -1461,7 +1462,7 @@
         <v>7553213</v>
       </c>
       <c r="B130" s="1">
-        <v>3018.6884000000009</v>
+        <v>3712.8804000000005</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
@@ -1469,7 +1470,7 @@
         <v>7554251</v>
       </c>
       <c r="B131" s="1">
-        <v>2030.0700000000013</v>
+        <v>2384.2976000000012</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
@@ -1477,7 +1478,7 @@
         <v>7554252</v>
       </c>
       <c r="B132" s="1">
-        <v>2303.56</v>
+        <v>2704.9133999999999</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
@@ -1485,7 +1486,7 @@
         <v>7563250</v>
       </c>
       <c r="B133" s="1">
-        <v>1542.2204999999999</v>
+        <v>1975.7865000000004</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
@@ -1493,7 +1494,7 @@
         <v>7227251</v>
       </c>
       <c r="B134" s="1">
-        <v>1828.8160000000014</v>
+        <v>2288.8242000000009</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
@@ -1501,7 +1502,7 @@
         <v>7227252</v>
       </c>
       <c r="B135" s="1">
-        <v>2013.3099999999995</v>
+        <v>2424.4028000000003</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
@@ -1509,7 +1510,7 @@
         <v>7651265</v>
       </c>
       <c r="B136" s="1">
-        <v>4421.3616000000029</v>
+        <v>4881.3408000000036</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
@@ -1517,7 +1518,7 @@
         <v>7586234</v>
       </c>
       <c r="B137" s="1">
-        <v>4419.8784000000023</v>
+        <v>5363.9124000000038</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
@@ -1525,7 +1526,7 @@
         <v>7586242</v>
       </c>
       <c r="B138" s="1">
-        <v>2177.3934000000008</v>
+        <v>2649.2321000000015</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
@@ -1533,7 +1534,7 @@
         <v>7586265</v>
       </c>
       <c r="B139" s="1">
-        <v>4267.1872000000021</v>
+        <v>5211.1654000000044</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
@@ -1557,7 +1558,7 @@
         <v>2824152</v>
       </c>
       <c r="B142" s="1">
-        <v>4325.45</v>
+        <v>5323.7039999999997</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
@@ -1565,7 +1566,7 @@
         <v>2824184</v>
       </c>
       <c r="B143" s="1">
-        <v>4800.9320000000034</v>
+        <v>5768.2100000000046</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
@@ -1573,7 +1574,7 @@
         <v>2825185</v>
       </c>
       <c r="B144" s="1">
-        <v>4745.2000000000016</v>
+        <v>5229.2750000000033</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
@@ -1581,7 +1582,7 @@
         <v>2825258</v>
       </c>
       <c r="B145" s="1">
-        <v>5925.1999999999989</v>
+        <v>6409.2749999999996</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
@@ -1589,7 +1590,7 @@
         <v>2825022</v>
       </c>
       <c r="B146" s="1">
-        <v>7095.54</v>
+        <v>7676.1239999999998</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
@@ -1597,7 +1598,7 @@
         <v>2825195</v>
       </c>
       <c r="B147" s="1">
-        <v>6438.6</v>
+        <v>6910.8423999999995</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
@@ -1605,7 +1606,7 @@
         <v>2825030</v>
       </c>
       <c r="B148" s="1">
-        <v>7203</v>
+        <v>7732.1216000000004</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
@@ -1613,7 +1614,7 @@
         <v>2828152</v>
       </c>
       <c r="B149" s="1">
-        <v>5304.0079999999998</v>
+        <v>6196.5660000000007</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
@@ -1621,7 +1622,7 @@
         <v>2828184</v>
       </c>
       <c r="B150" s="1">
-        <v>5825.2160000000049</v>
+        <v>6816.4880000000039</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
@@ -1629,7 +1630,7 @@
         <v>2828229</v>
       </c>
       <c r="B151" s="1">
-        <v>5943.2160000000003</v>
+        <v>6934.4879999999994</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
@@ -1637,7 +1638,7 @@
         <v>2828230</v>
       </c>
       <c r="B152" s="1">
-        <v>5410.2080000000005</v>
+        <v>5886.9120000000003</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
@@ -1645,7 +1646,7 @@
         <v>2829152</v>
       </c>
       <c r="B153" s="1">
-        <v>5304.0079999999998</v>
+        <v>5780.7119999999995</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
@@ -1653,7 +1654,7 @@
         <v>2829184</v>
       </c>
       <c r="B154" s="1">
-        <v>5825.2160000000049</v>
+        <v>6816.4880000000039</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
@@ -1661,7 +1662,7 @@
         <v>2829229</v>
       </c>
       <c r="B155" s="1">
-        <v>5943.2160000000003</v>
+        <v>6934.4879999999994</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
@@ -1669,7 +1670,7 @@
         <v>2829230</v>
       </c>
       <c r="B156" s="1">
-        <v>5410.2080000000005</v>
+        <v>6302.7660000000005</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
@@ -1677,7 +1678,7 @@
         <v>2830230</v>
       </c>
       <c r="B157" s="1">
-        <v>5410.2080000000005</v>
+        <v>6302.7660000000005</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
@@ -1685,7 +1686,7 @@
         <v>2830229</v>
       </c>
       <c r="B158" s="1">
-        <v>5943.2160000000003</v>
+        <v>6934.4879999999994</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
@@ -1693,7 +1694,7 @@
         <v>2885036</v>
       </c>
       <c r="B159" s="1">
-        <v>4281.5199999999995</v>
+        <v>4890.2180000000008</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
@@ -1701,7 +1702,7 @@
         <v>2889156</v>
       </c>
       <c r="B160" s="1">
-        <v>3913.2400000000002</v>
+        <v>4724.9439999999995</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
@@ -1709,7 +1710,7 @@
         <v>2924152</v>
       </c>
       <c r="B161" s="1">
-        <v>4413.04</v>
+        <v>4951.6359999999995</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
@@ -1717,7 +1718,7 @@
         <v>2924184</v>
       </c>
       <c r="B162" s="1">
-        <v>4902.800000000002</v>
+        <v>5940.9000000000042</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
@@ -1725,7 +1726,7 @@
         <v>2924229</v>
       </c>
       <c r="B163" s="1">
-        <v>5185.9999999999991</v>
+        <v>6200.5000000000009</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
@@ -1733,7 +1734,7 @@
         <v>2924230</v>
       </c>
       <c r="B164" s="1">
-        <v>4667.92</v>
+        <v>5581.1500000000015</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
@@ -1741,7 +1742,7 @@
         <v>2931184</v>
       </c>
       <c r="B165" s="1">
-        <v>5123.4100000000035</v>
+        <v>6232.0800000000045</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
@@ -1749,7 +1750,7 @@
         <v>2931225</v>
       </c>
       <c r="B166" s="1">
-        <v>6273.2960000000003</v>
+        <v>7462.5439999999981</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
@@ -1757,7 +1758,7 @@
         <v>2931229</v>
       </c>
       <c r="B167" s="1">
-        <v>5241.41</v>
+        <v>6232.08</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
@@ -1765,7 +1766,7 @@
         <v>2936152</v>
       </c>
       <c r="B168" s="1">
-        <v>4411.5479999999989</v>
+        <v>5409.6</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
@@ -1773,7 +1774,7 @@
         <v>2936229</v>
       </c>
       <c r="B169" s="1">
-        <v>4890.4800000000005</v>
+        <v>5999.1080000000002</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
@@ -1781,7 +1782,7 @@
         <v>2936230</v>
       </c>
       <c r="B170" s="1">
-        <v>4411.5479999999989</v>
+        <v>5409.6</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
@@ -1789,7 +1790,7 @@
         <v>2944229</v>
       </c>
       <c r="B171" s="1">
-        <v>5626.8499999999995</v>
+        <v>6594.4840000000004</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
@@ -1797,7 +1798,7 @@
         <v>2944230</v>
       </c>
       <c r="B172" s="1">
-        <v>5069.0659999999989</v>
+        <v>5939.46</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
@@ -1805,7 +1806,7 @@
         <v>2949184</v>
       </c>
       <c r="B173" s="1">
-        <v>7737.2000000000062</v>
+        <v>8704.4500000000062</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
@@ -1813,7 +1814,7 @@
         <v>2971195</v>
       </c>
       <c r="B174" s="1">
-        <v>2637.3231999999998</v>
+        <v>3121.0744</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
@@ -1821,7 +1822,7 @@
         <v>2971225</v>
       </c>
       <c r="B175" s="1">
-        <v>6537.6600000000017</v>
+        <v>7698.655999999999</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
@@ -1829,7 +1830,7 @@
         <v>2967204</v>
       </c>
       <c r="B176" s="1">
-        <v>3889.2212000000009</v>
+        <v>4484.2015999999994</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
@@ -1837,7 +1838,7 @@
         <v>2967213</v>
       </c>
       <c r="B177" s="1">
-        <v>4362.4600000000019</v>
+        <v>5056.5760000000009</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
@@ -1845,7 +1846,7 @@
         <v>2967111</v>
       </c>
       <c r="B178" s="1">
-        <v>4445.0600000000004</v>
+        <v>5221.7759999999998</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
@@ -1853,7 +1854,7 @@
         <v>2967184</v>
       </c>
       <c r="B179" s="1">
-        <v>6782.5740000000042</v>
+        <v>7773.8400000000047</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
@@ -1861,7 +1862,7 @@
         <v>7211213</v>
       </c>
       <c r="B180" s="1">
-        <v>4197.2192000000005</v>
+        <v>4874.4680000000008</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
@@ -1869,7 +1870,7 @@
         <v>7271213</v>
       </c>
       <c r="B181" s="1">
-        <v>6166.8320000000031</v>
+        <v>6679.4096000000009</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
@@ -1877,7 +1878,7 @@
         <v>7271111</v>
       </c>
       <c r="B182" s="1">
-        <v>6166.8320000000012</v>
+        <v>6844.6095999999998</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
@@ -1885,7 +1886,7 @@
         <v>7275185</v>
       </c>
       <c r="B183" s="1">
-        <v>7244.4000000000033</v>
+        <v>7715.9550000000045</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
@@ -1893,7 +1894,7 @@
         <v>7275111</v>
       </c>
       <c r="B184" s="1">
-        <v>10139.582399999999</v>
+        <v>10799.138400000002</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
@@ -1901,7 +1902,7 @@
         <v>7275220</v>
       </c>
       <c r="B185" s="1">
-        <v>11588.4624</v>
+        <v>12342.896400000001</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
@@ -1909,7 +1910,7 @@
         <v>2900103</v>
       </c>
       <c r="B186" s="1">
-        <v>4146.1200000000008</v>
+        <v>4712.1480000000001</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
@@ -1917,7 +1918,7 @@
         <v>2900125</v>
       </c>
       <c r="B187" s="1">
-        <v>3807</v>
+        <v>4373.5020000000004</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
@@ -1925,7 +1926,7 @@
         <v>2900145</v>
       </c>
       <c r="B188" s="1">
-        <v>3598.12</v>
+        <v>4164.6359999999995</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
@@ -1933,7 +1934,7 @@
         <v>2900165</v>
       </c>
       <c r="B189" s="1">
-        <v>1485.2720000000002</v>
+        <v>1721.1399999999999</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
@@ -1941,7 +1942,7 @@
         <v>2900175</v>
       </c>
       <c r="B190" s="1">
-        <v>2931.2960000000012</v>
+        <v>3161.4800000000018</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
@@ -1949,7 +1950,7 @@
         <v>2900184</v>
       </c>
       <c r="B191" s="1">
-        <v>5741.9880000000039</v>
+        <v>6186.3600000000051</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
@@ -1957,7 +1958,7 @@
         <v>7701341</v>
       </c>
       <c r="B192" s="1">
-        <v>5203.988400000002</v>
+        <v>5630.087300000002</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
@@ -1965,7 +1966,7 @@
         <v>7705303</v>
       </c>
       <c r="B193" s="1">
-        <v>2981.0999999999995</v>
+        <v>3453.2439999999983</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
@@ -1973,7 +1974,7 @@
         <v>7705313</v>
       </c>
       <c r="B194" s="1">
-        <v>2967.3</v>
+        <v>3439.395</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
@@ -1981,7 +1982,7 @@
         <v>7705327</v>
       </c>
       <c r="B195" s="1">
-        <v>3490.0560000000014</v>
+        <v>4056.1380000000022</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
@@ -1989,7 +1990,7 @@
         <v>7705337</v>
       </c>
       <c r="B196" s="1">
-        <v>3440.7699999999995</v>
+        <v>4007.1</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
@@ -1997,7 +1998,7 @@
         <v>7705339</v>
       </c>
       <c r="B197" s="1">
-        <v>1394.8370000000002</v>
+        <v>1630.7295000000001</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
@@ -2005,7 +2006,7 @@
         <v>7705340</v>
       </c>
       <c r="B198" s="1">
-        <v>2789.6740000000004</v>
+        <v>3261.4590000000003</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
@@ -2013,7 +2014,7 @@
         <v>7705341</v>
       </c>
       <c r="B199" s="1">
-        <v>5128.8000000000029</v>
+        <v>6072.4600000000028</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
@@ -2021,7 +2022,7 @@
         <v>7727303</v>
       </c>
       <c r="B200" s="1">
-        <v>3245.6819999999998</v>
+        <v>3539.5419999999986</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
@@ -2029,7 +2030,7 @@
         <v>7727313</v>
       </c>
       <c r="B201" s="1">
-        <v>3070.07</v>
+        <v>3660.1800000000007</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
@@ -2037,7 +2038,7 @@
         <v>7727327</v>
       </c>
       <c r="B202" s="1">
-        <v>3586.9680000000017</v>
+        <v>4295.0340000000006</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
@@ -2045,7 +2046,7 @@
         <v>7727337</v>
       </c>
       <c r="B203" s="1">
-        <v>3476.1779999999994</v>
+        <v>4254.5999999999985</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
@@ -2053,7 +2054,7 @@
         <v>7727341</v>
       </c>
       <c r="B204" s="1">
-        <v>5553.5100000000029</v>
+        <v>6850.9200000000028</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
@@ -2061,7 +2062,7 @@
         <v>7849303</v>
       </c>
       <c r="B205" s="1">
-        <v>3266.72</v>
+        <v>3642.3679999999995</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
@@ -2069,7 +2070,7 @@
         <v>7849313</v>
       </c>
       <c r="B206" s="1">
-        <v>3794.96</v>
+        <v>4266.8799999999992</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
@@ -2077,7 +2078,7 @@
         <v>7849327</v>
       </c>
       <c r="B207" s="1">
-        <v>3756.7200000000012</v>
+        <v>4465.0800000000017</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
@@ -2085,7 +2086,7 @@
         <v>7849337</v>
       </c>
       <c r="B208" s="1">
-        <v>3719.6980000000003</v>
+        <v>4428.2</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
@@ -2093,7 +2094,7 @@
         <v>7849340</v>
       </c>
       <c r="B209" s="1">
-        <v>3056.7150000000001</v>
+        <v>3646.8</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
@@ -2101,7 +2102,7 @@
         <v>7849341</v>
       </c>
       <c r="B210" s="1">
-        <v>5899.4900000000025</v>
+        <v>7079.3200000000043</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
@@ -2109,7 +2110,7 @@
         <v>7849343</v>
       </c>
       <c r="B211" s="1">
-        <v>2110.34</v>
+        <v>2523.1295000000005</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
@@ -2117,7 +2118,7 @@
         <v>7849344</v>
       </c>
       <c r="B212" s="1">
-        <v>2986.5</v>
+        <v>3576.2600000000007</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
@@ -2125,7 +2126,7 @@
         <v>7903303</v>
       </c>
       <c r="B213" s="1">
-        <v>3848.04</v>
+        <v>4319.9919999999993</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
@@ -2133,7 +2134,7 @@
         <v>7903313</v>
       </c>
       <c r="B214" s="1">
-        <v>3138.8</v>
+        <v>3670.1</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
@@ -2141,7 +2142,7 @@
         <v>7903327</v>
       </c>
       <c r="B215" s="1">
-        <v>4462.9200000000019</v>
+        <v>4764.7440000000006</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
@@ -2149,7 +2150,7 @@
         <v>7903337</v>
       </c>
       <c r="B216" s="1">
-        <v>4426.655999999999</v>
+        <v>4728.33</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
@@ -2157,7 +2158,7 @@
         <v>7903339</v>
       </c>
       <c r="B217" s="1">
-        <v>1834.4300000000003</v>
+        <v>2070.6</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
@@ -2165,7 +2166,7 @@
         <v>7903343</v>
       </c>
       <c r="B218" s="1">
-        <v>2554.335</v>
+        <v>2884.6125000000002</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
@@ -2173,7 +2174,7 @@
         <v>7903344</v>
       </c>
       <c r="B219" s="1">
-        <v>3618.83</v>
+        <v>4090.9</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
@@ -2181,7 +2182,7 @@
         <v>7903341</v>
       </c>
       <c r="B220" s="1">
-        <v>7059.6900000000023</v>
+        <v>8003.8800000000037</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
@@ -2189,7 +2190,7 @@
         <v>2909165</v>
       </c>
       <c r="B221" s="1">
-        <v>1759.12</v>
+        <v>1995.0299999999997</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
@@ -2197,7 +2198,7 @@
         <v>2909175</v>
       </c>
       <c r="B222" s="1">
-        <v>3401.3280000000013</v>
+        <v>3873.2700000000023</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
@@ -2205,7 +2206,7 @@
         <v>6488184</v>
       </c>
       <c r="B223" s="1">
-        <v>2500.0000000000018</v>
+        <v>3443.8300000000022</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
@@ -2213,7 +2214,7 @@
         <v>6489184</v>
       </c>
       <c r="B224" s="1">
-        <v>2025.0000000000014</v>
+        <v>2968.9200000000019</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
@@ -2221,7 +2222,7 @@
         <v>7584165</v>
       </c>
       <c r="B225" s="1">
-        <v>1575.6</v>
+        <v>1811.5020000000002</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
@@ -2229,7 +2230,7 @@
         <v>7584175</v>
       </c>
       <c r="B226" s="1">
-        <v>3151.3720000000017</v>
+        <v>3623.2320000000018</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
@@ -2237,7 +2238,7 @@
         <v>7584184</v>
       </c>
       <c r="B227" s="1">
-        <v>5752.7600000000039</v>
+        <v>6696.440000000006</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
@@ -2245,7 +2246,7 @@
         <v>7584185</v>
       </c>
       <c r="B228" s="1">
-        <v>2876.3800000000015</v>
+        <v>3348.2200000000025</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
@@ -2253,7 +2254,7 @@
         <v>7607185</v>
       </c>
       <c r="B229" s="1">
-        <v>2076.3000000000011</v>
+        <v>2548.3500000000013</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
@@ -2261,7 +2262,7 @@
         <v>2914165</v>
       </c>
       <c r="B230" s="1">
-        <v>2257.1640000000002</v>
+        <v>2493.0509999999999</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
@@ -2269,7 +2270,7 @@
         <v>2914175</v>
       </c>
       <c r="B231" s="1">
-        <v>4325.8480000000027</v>
+        <v>4797.6500000000024</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
@@ -2277,7 +2278,7 @@
         <v>7607184</v>
       </c>
       <c r="B232" s="1">
-        <v>4152.6000000000031</v>
+        <v>5096.7000000000035</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
@@ -2285,7 +2286,7 @@
         <v>3001265</v>
       </c>
       <c r="B233" s="1">
-        <v>3010.3590000000022</v>
+        <v>5582.586000000003</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
@@ -2293,7 +2294,7 @@
         <v>3002265</v>
       </c>
       <c r="B234" s="1">
-        <v>3077.0238000000031</v>
+        <v>5649.4008000000022</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
@@ -2301,7 +2302,7 @@
         <v>3006234</v>
       </c>
       <c r="B235" s="1">
-        <v>3421.2192000000023</v>
+        <v>6064.7328000000043</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
@@ -2309,7 +2310,7 @@
         <v>3006265</v>
       </c>
       <c r="B236" s="1">
-        <v>3171.1360000000013</v>
+        <v>5884.9132000000045</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
@@ -2317,7 +2318,7 @@
         <v>3020265</v>
       </c>
       <c r="B237" s="1">
-        <v>4322.247400000002</v>
+        <v>5714.6373000000031</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
@@ -2325,7 +2326,7 @@
         <v>3614265</v>
       </c>
       <c r="B238" s="1">
-        <v>4225.9100000000035</v>
+        <v>6208.3380000000052</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
@@ -2333,7 +2334,7 @@
         <v>3617265</v>
       </c>
       <c r="B239" s="1">
-        <v>4345.1097000000036</v>
+        <v>6021.0839000000042</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
@@ -2341,7 +2342,7 @@
         <v>3040265</v>
       </c>
       <c r="B240" s="1">
-        <v>2619.7000000000016</v>
+        <v>4365.7650000000031</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
@@ -2357,7 +2358,7 @@
         <v>3059265</v>
       </c>
       <c r="B242" s="1">
-        <v>4834.7899000000034</v>
+        <v>6085.5899000000036</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
@@ -2365,7 +2366,7 @@
         <v>3064265</v>
       </c>
       <c r="B243" s="1">
-        <v>5408.2028000000037</v>
+        <v>6399.422400000004</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
@@ -2373,7 +2374,7 @@
         <v>3084265</v>
       </c>
       <c r="B244" s="1">
-        <v>3562.2280000000023</v>
+        <v>6016.3674000000037</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
@@ -2381,7 +2382,7 @@
         <v>4501265</v>
       </c>
       <c r="B245" s="1">
-        <v>3474.7018000000021</v>
+        <v>5669.3106000000034</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
@@ -2389,7 +2390,7 @@
         <v>7403265</v>
       </c>
       <c r="B246" s="1">
-        <v>3730.8540000000021</v>
+        <v>4675.1565000000028</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
@@ -2453,7 +2454,7 @@
         <v>7330242</v>
       </c>
       <c r="B254" s="1">
-        <v>586.25000000000023</v>
+        <v>904.90400000000056</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
@@ -2461,7 +2462,7 @@
         <v>7330265</v>
       </c>
       <c r="B255" s="1">
-        <v>1137.5000000000007</v>
+        <v>1727.5500000000011</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
@@ -2469,7 +2470,7 @@
         <v>2874152</v>
       </c>
       <c r="B256" s="1">
-        <v>3020.7200000000003</v>
+        <v>3999.76</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
@@ -2477,7 +2478,7 @@
         <v>2874184</v>
       </c>
       <c r="B257" s="1">
-        <v>3355.9680000000026</v>
+        <v>4443.9840000000031</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
@@ -2485,7 +2486,7 @@
         <v>7364184</v>
       </c>
       <c r="B258" s="1">
-        <v>3449.0000000000023</v>
+        <v>4392.5500000000029</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
@@ -2493,7 +2494,7 @@
         <v>7364203</v>
       </c>
       <c r="B259" s="1">
-        <v>2069.3880000000008</v>
+        <v>2635.7940000000017</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
@@ -2501,7 +2502,7 @@
         <v>7364234</v>
       </c>
       <c r="B260" s="1">
-        <v>3448.9800000000023</v>
+        <v>4392.9900000000025</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
@@ -2509,7 +2510,7 @@
         <v>7364242</v>
       </c>
       <c r="B261" s="1">
-        <v>1724.5250000000008</v>
+        <v>2196.4800000000009</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
@@ -2517,7 +2518,7 @@
         <v>7364251</v>
       </c>
       <c r="B262" s="1">
-        <v>1293.367500000001</v>
+        <v>1647.2473000000009</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
@@ -2525,7 +2526,7 @@
         <v>7364256</v>
       </c>
       <c r="B263" s="1">
-        <v>2586.7875000000017</v>
+        <v>3294.7200000000025</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
@@ -2533,7 +2534,7 @@
         <v>7364265</v>
       </c>
       <c r="B264" s="1">
-        <v>3449.0500000000025</v>
+        <v>4392.9600000000028</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
@@ -2541,7 +2542,7 @@
         <v>7370184</v>
       </c>
       <c r="B265" s="1">
-        <v>3778.2000000000025</v>
+        <v>4722.3600000000033</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
@@ -2549,7 +2550,7 @@
         <v>7370234</v>
       </c>
       <c r="B266" s="1">
-        <v>3777.7300000000027</v>
+        <v>4722.2000000000025</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
@@ -2557,7 +2558,7 @@
         <v>7370242</v>
       </c>
       <c r="B267" s="1">
-        <v>1889.1400000000008</v>
+        <v>2361.1050000000014</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
@@ -2565,7 +2566,7 @@
         <v>7370251</v>
       </c>
       <c r="B268" s="1">
-        <v>1416.8550000000009</v>
+        <v>1770.8950000000011</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
@@ -2573,7 +2574,7 @@
         <v>7370256</v>
       </c>
       <c r="B269" s="1">
-        <v>2833.7100000000019</v>
+        <v>3541.6575000000016</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
@@ -2581,7 +2582,7 @@
         <v>7376184</v>
       </c>
       <c r="B270" s="1">
-        <v>3396.0600000000022</v>
+        <v>3926.7300000000027</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
@@ -2589,7 +2590,7 @@
         <v>7376251</v>
       </c>
       <c r="B271" s="1">
-        <v>1273.650000000001</v>
+        <v>1477.3988000000008</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
@@ -2597,7 +2598,7 @@
         <v>2502184</v>
       </c>
       <c r="B272" s="1">
-        <v>5057.3100000000031</v>
+        <v>5561.1400000000031</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
@@ -2605,7 +2606,7 @@
         <v>2502174</v>
       </c>
       <c r="B273" s="1">
-        <v>5419.1600000000026</v>
+        <v>6410.3200000000024</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
@@ -2613,7 +2614,7 @@
         <v>2960401</v>
       </c>
       <c r="B274" s="1">
-        <v>147440.99999999997</v>
+        <v>157353</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
@@ -2621,7 +2622,7 @@
         <v>2960401</v>
       </c>
       <c r="B275" s="1">
-        <v>147440.99999999997</v>
+        <v>157353</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
@@ -2629,7 +2630,7 @@
         <v>7427401</v>
       </c>
       <c r="B276" s="1">
-        <v>74340</v>
+        <v>80535</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
@@ -2637,7 +2638,7 @@
         <v>7428401</v>
       </c>
       <c r="B277" s="1">
-        <v>82517.399999999994</v>
+        <v>88712.4</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
@@ -2645,7 +2646,7 @@
         <v>7670401</v>
       </c>
       <c r="B278" s="1">
-        <v>54515.999999999993</v>
+        <v>60710.999999999993</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
@@ -2653,7 +2654,7 @@
         <v>7688401</v>
       </c>
       <c r="B279" s="1">
-        <v>57737.4</v>
+        <v>63932.4</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
@@ -2773,7 +2774,7 @@
         <v>7264401</v>
       </c>
       <c r="B294" s="1">
-        <v>71862</v>
+        <v>75331.199999999997</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
@@ -2781,7 +2782,7 @@
         <v>7267401</v>
       </c>
       <c r="B295" s="1">
-        <v>166769.4</v>
+        <v>171725.4</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
@@ -2789,7 +2790,7 @@
         <v>7265401</v>
       </c>
       <c r="B296" s="1">
-        <v>104819.4</v>
+        <v>109775.40000000001</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
@@ -2797,7 +2798,7 @@
         <v>1301401</v>
       </c>
       <c r="B297" s="1">
-        <v>45843</v>
+        <v>56498.399999999994</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
@@ -2805,7 +2806,7 @@
         <v>1404401</v>
       </c>
       <c r="B298" s="1">
-        <v>55011.6</v>
+        <v>65667</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
@@ -2813,7 +2814,7 @@
         <v>7436401</v>
       </c>
       <c r="B299" s="1">
-        <v>59224.2</v>
+        <v>69631.8</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
@@ -2821,7 +2822,7 @@
         <v>7470401</v>
       </c>
       <c r="B300" s="1">
-        <v>46834.2</v>
+        <v>56993.999999999993</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
@@ -2829,7 +2830,7 @@
         <v>7472401</v>
       </c>
       <c r="B301" s="1">
-        <v>46338.6</v>
+        <v>57241.799999999996</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
@@ -2837,7 +2838,7 @@
         <v>7485401</v>
       </c>
       <c r="B302" s="1">
-        <v>43117.2</v>
+        <v>54020.4</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
@@ -2845,7 +2846,7 @@
         <v>7489271</v>
       </c>
       <c r="B303" s="1">
-        <v>13275</v>
+        <v>16047.999999999998</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
@@ -2853,7 +2854,7 @@
         <v>7489401</v>
       </c>
       <c r="B304" s="1">
-        <v>55259.399999999994</v>
+        <v>66906</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
@@ -2861,7 +2862,7 @@
         <v>7494401</v>
       </c>
       <c r="B305" s="1">
-        <v>53029.2</v>
+        <v>62941.2</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
@@ -2869,7 +2870,7 @@
         <v>7577271</v>
       </c>
       <c r="B306" s="1">
-        <v>11918</v>
+        <v>14395.999999999998</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
@@ -2877,7 +2878,7 @@
         <v>7577401</v>
       </c>
       <c r="B307" s="1">
-        <v>49807.799999999996</v>
+        <v>59967.6</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
@@ -2885,7 +2886,7 @@
         <v>7612401</v>
       </c>
       <c r="B308" s="1">
-        <v>50551.199999999997</v>
+        <v>60710.999999999993</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
@@ -2893,7 +2894,7 @@
         <v>2502401</v>
       </c>
       <c r="B309" s="1">
-        <v>51542.400000000001</v>
+        <v>61950</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
@@ -2901,7 +2902,7 @@
         <v>2503401</v>
       </c>
       <c r="B310" s="1">
-        <v>56746.2</v>
+        <v>67153.799999999988</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
@@ -2909,7 +2910,7 @@
         <v>4906401</v>
       </c>
       <c r="B311" s="1">
-        <v>42621.599999999999</v>
+        <v>54268.19999999999</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
@@ -2917,7 +2918,7 @@
         <v>4925401</v>
       </c>
       <c r="B312" s="1">
-        <v>48073.2</v>
+        <v>58233</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
@@ -2925,7 +2926,7 @@
         <v>7511401</v>
       </c>
       <c r="B313" s="1">
-        <v>53772.6</v>
+        <v>64180.200000000004</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
@@ -2933,7 +2934,7 @@
         <v>7515401</v>
       </c>
       <c r="B314" s="1">
-        <v>55755</v>
+        <v>66162.600000000006</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
@@ -2941,7 +2942,7 @@
         <v>4950288</v>
       </c>
       <c r="B315" s="1">
-        <v>5092.88</v>
+        <v>6688.24</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
@@ -2949,7 +2950,7 @@
         <v>4950401</v>
       </c>
       <c r="B316" s="1">
-        <v>49064.399999999994</v>
+        <v>58976.399999999994</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
@@ -2957,7 +2958,7 @@
         <v>7651401</v>
       </c>
       <c r="B317" s="1">
-        <v>39152.400000000001</v>
+        <v>49064.399999999994</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
@@ -2965,7 +2966,7 @@
         <v>2900401</v>
       </c>
       <c r="B318" s="1">
-        <v>59219.243999999999</v>
+        <v>69131.243999999992</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
@@ -2973,7 +2974,7 @@
         <v>2900403</v>
       </c>
       <c r="B319" s="1">
-        <v>59219.243999999999</v>
+        <v>69131.243999999992</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
@@ -2981,7 +2982,7 @@
         <v>7701451</v>
       </c>
       <c r="B320" s="1">
-        <v>50253.840000000004</v>
+        <v>58844.24</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
@@ -2989,7 +2990,7 @@
         <v>7705451</v>
       </c>
       <c r="B321" s="1">
-        <v>50468.6</v>
+        <v>59059</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
@@ -2997,7 +2998,7 @@
         <v>7727451</v>
       </c>
       <c r="B322" s="1">
-        <v>67649.399999999994</v>
+        <v>76239.8</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
@@ -3005,7 +3006,7 @@
         <v>7849451</v>
       </c>
       <c r="B323" s="1">
-        <v>71300.319999999992</v>
+        <v>79890.720000000001</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
@@ -3013,7 +3014,7 @@
         <v>7903451</v>
       </c>
       <c r="B324" s="1">
-        <v>70226.51999999999</v>
+        <v>79461.2</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
@@ -3021,7 +3022,7 @@
         <v>7584401</v>
       </c>
       <c r="B325" s="1">
-        <v>50551.199999999997</v>
+        <v>60463.19999999999</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
@@ -3029,7 +3030,7 @@
         <v>2909401</v>
       </c>
       <c r="B326" s="1">
-        <v>63436.799999999996</v>
+        <v>73348.799999999988</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
@@ -3037,7 +3038,7 @@
         <v>7742451</v>
       </c>
       <c r="B327" s="1">
-        <v>50683.359999999993</v>
+        <v>68723.199999999997</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
@@ -3045,7 +3046,7 @@
         <v>3040288</v>
       </c>
       <c r="B328" s="1">
-        <v>3344.12</v>
+        <v>5614.44</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
@@ -3053,7 +3054,7 @@
         <v>3006271</v>
       </c>
       <c r="B329" s="1">
-        <v>7847</v>
+        <v>14632</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
@@ -3061,7 +3062,7 @@
         <v>3006288</v>
       </c>
       <c r="B330" s="1">
-        <v>4111.12</v>
+        <v>7639.32</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
@@ -3069,7 +3070,7 @@
         <v>3001401</v>
       </c>
       <c r="B331" s="1">
-        <v>30479.399999999998</v>
+        <v>49560</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
@@ -3077,7 +3078,7 @@
         <v>3002401</v>
       </c>
       <c r="B332" s="1">
-        <v>31966.2</v>
+        <v>50798.999999999993</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
@@ -3085,7 +3086,7 @@
         <v>3006401</v>
       </c>
       <c r="B333" s="1">
-        <v>32461.799999999996</v>
+        <v>53277</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
@@ -3093,7 +3094,7 @@
         <v>3007403</v>
       </c>
       <c r="B334" s="1">
-        <v>38904.6</v>
+        <v>61950</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
@@ -3101,7 +3102,7 @@
         <v>3020401</v>
       </c>
       <c r="B335" s="1">
-        <v>43365</v>
+        <v>58976.399999999994</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
@@ -3109,144 +3110,137 @@
         <v>3017401</v>
       </c>
       <c r="B336" s="1">
-        <v>47329.799999999996</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+        <v>61206.6</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>3019401</v>
       </c>
       <c r="B337" s="1">
-        <v>40639.199999999997</v>
-      </c>
-    </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+        <v>57241.799999999996</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>3064401</v>
       </c>
       <c r="B338" s="1">
-        <v>44851.799999999996</v>
-      </c>
-    </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+        <v>56250.600000000006</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>3081401</v>
       </c>
       <c r="B339" s="1">
-        <v>48568.800000000003</v>
-      </c>
-    </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+        <v>58480.799999999988</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>3082401</v>
       </c>
       <c r="B340" s="1">
-        <v>35931</v>
-      </c>
-    </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+        <v>59719.799999999996</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>3084401</v>
       </c>
       <c r="B341" s="1">
-        <v>35435.399999999994</v>
-      </c>
-    </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+        <v>62197.8</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>3121401</v>
       </c>
       <c r="B342" s="1">
-        <v>49560</v>
-      </c>
-    </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+        <v>59472</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>3122401</v>
       </c>
       <c r="B343" s="1">
-        <v>50798.999999999993</v>
-      </c>
-    </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+        <v>60710.999999999993</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>3614401</v>
       </c>
       <c r="B344" s="1">
-        <v>41878.199999999997</v>
-      </c>
-    </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+        <v>63684.6</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>3617401</v>
       </c>
       <c r="B345" s="1">
-        <v>43117.2</v>
-      </c>
-    </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+        <v>61702.2</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>3923401</v>
       </c>
       <c r="B346" s="1">
-        <v>36922.199999999997</v>
-      </c>
-    </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+        <v>52285.799999999996</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>4803401</v>
       </c>
       <c r="B347" s="1">
-        <v>29736</v>
-      </c>
-    </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+        <v>53772.6</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
         <v>4811401</v>
       </c>
       <c r="B348" s="1">
-        <v>34692</v>
-      </c>
-    </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+        <v>56993.999999999993</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>4501401</v>
       </c>
       <c r="B349" s="1">
-        <v>32957.4</v>
-      </c>
-    </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+        <v>56993.999999999993</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>7403401</v>
       </c>
       <c r="B350" s="1">
-        <v>29736</v>
-      </c>
-    </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+        <v>39648</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>7330403</v>
       </c>
       <c r="B351" s="1">
-        <v>10903.199999999999</v>
-      </c>
-    </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+        <v>17098.2</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
-        <v>7577240</v>
+        <v>7079401</v>
       </c>
       <c r="B352" s="1">
-        <v>4550.5</v>
-      </c>
-    </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A353" s="1">
-        <v>7079401</v>
-      </c>
-      <c r="B353" s="1">
         <v>92677.2</v>
       </c>
+      <c r="C352" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
